--- a/Outputs/Scenarios/PtX_demand_LT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LT_Electrification.xlsx
@@ -806,7 +806,7 @@
         <v>4.448074282126064e-06</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0008573152441552001</v>
+        <v>0.0008573152441552002</v>
       </c>
       <c r="I10" t="n">
         <v>0.001591596591314699</v>
@@ -843,7 +843,7 @@
         <v>3.132648279294923e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0078353990726053</v>
+        <v>0.007835399072605302</v>
       </c>
       <c r="I11" t="n">
         <v>0.0102817325873576</v>
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.007631242559749887</v>
+        <v>0.007631242559749886</v>
       </c>
     </row>
     <row r="33">

--- a/Outputs/Scenarios/PtX_demand_LT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LT_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.003207264563663378</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001944452397836342</v>
+        <v>0.002073255167090504</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0003240753996393903</v>
+        <v>0.0004290013576633362</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001296301598557561</v>
+        <v>0.001716005430653345</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001944452397836342</v>
+        <v>0.001716005430653345</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0002570307802572764</v>
       </c>
       <c r="K24" t="n">
-        <v>0.00269301884919264</v>
+        <v>0.002643891311774204</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.001555807853643541</v>
       </c>
       <c r="K25" t="n">
-        <v>0.02635508468139328</v>
+        <v>0.02587430066859687</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>4.62112533740057e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0003240753996393903</v>
+        <v>0.0004290013576633362</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.004747964713591852</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01144686383962483</v>
+        <v>0.01118871631465711</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.001907810639937472</v>
+        <v>0.002315187520421738</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.007631242559749886</v>
+        <v>0.009260750081686952</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01144686383962483</v>
+        <v>0.009260750081686952</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0002498928796627291</v>
       </c>
       <c r="K42" t="n">
-        <v>0.001907810639937472</v>
+        <v>0.002315187520421738</v>
       </c>
     </row>
     <row r="43">
